--- a/output/yearly_population_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_48_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5834</v>
+        <v>6437</v>
       </c>
       <c r="C2" t="n">
-        <v>6063</v>
+        <v>5421</v>
       </c>
       <c r="D2" t="n">
-        <v>22873</v>
+        <v>26804</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3958</v>
+        <v>4012</v>
       </c>
       <c r="C3" t="n">
-        <v>4424</v>
+        <v>6772</v>
       </c>
       <c r="D3" t="n">
-        <v>14457</v>
+        <v>13616</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2804</v>
+        <v>3201</v>
       </c>
       <c r="C4" t="n">
-        <v>6346</v>
+        <v>6504</v>
       </c>
       <c r="D4" t="n">
-        <v>6801</v>
+        <v>5833</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1829</v>
+        <v>2135</v>
       </c>
       <c r="C5" t="n">
-        <v>5828</v>
+        <v>5146</v>
       </c>
       <c r="D5" t="n">
-        <v>2487</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1082</v>
+        <v>1271</v>
       </c>
       <c r="C6" t="n">
-        <v>3593</v>
+        <v>4062</v>
       </c>
       <c r="D6" t="n">
-        <v>1070</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>509</v>
+        <v>640</v>
       </c>
       <c r="C7" t="n">
-        <v>1869</v>
+        <v>2435</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="C8" t="n">
-        <v>820</v>
+        <v>1005</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6255</v>
+        <v>7285</v>
       </c>
       <c r="C2" t="n">
-        <v>9415</v>
+        <v>15958</v>
       </c>
       <c r="D2" t="n">
-        <v>22096</v>
+        <v>24506</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3903</v>
+        <v>4110</v>
       </c>
       <c r="C3" t="n">
-        <v>4542</v>
+        <v>5462</v>
       </c>
       <c r="D3" t="n">
-        <v>14630</v>
+        <v>14410</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2816</v>
+        <v>3058</v>
       </c>
       <c r="C4" t="n">
-        <v>5248</v>
+        <v>6492</v>
       </c>
       <c r="D4" t="n">
-        <v>7843</v>
+        <v>6795</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2003</v>
+        <v>2279</v>
       </c>
       <c r="C5" t="n">
-        <v>5945</v>
+        <v>5589</v>
       </c>
       <c r="D5" t="n">
-        <v>3050</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1272</v>
+        <v>1481</v>
       </c>
       <c r="C6" t="n">
-        <v>4510</v>
+        <v>4492</v>
       </c>
       <c r="D6" t="n">
-        <v>1273</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>670</v>
+        <v>807</v>
       </c>
       <c r="C7" t="n">
-        <v>2628</v>
+        <v>3095</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>285</v>
+        <v>353</v>
       </c>
       <c r="C8" t="n">
-        <v>1253</v>
+        <v>1583</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8445</v>
+        <v>8353</v>
       </c>
       <c r="C2" t="n">
-        <v>12319</v>
+        <v>15610</v>
       </c>
       <c r="D2" t="n">
-        <v>24058</v>
+        <v>19830</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3946</v>
+        <v>4339</v>
       </c>
       <c r="C3" t="n">
-        <v>5787</v>
+        <v>8478</v>
       </c>
       <c r="D3" t="n">
-        <v>14589</v>
+        <v>14699</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2765</v>
+        <v>2954</v>
       </c>
       <c r="C4" t="n">
-        <v>4833</v>
+        <v>5869</v>
       </c>
       <c r="D4" t="n">
-        <v>8506</v>
+        <v>7684</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2066</v>
+        <v>2301</v>
       </c>
       <c r="C5" t="n">
-        <v>5476</v>
+        <v>5783</v>
       </c>
       <c r="D5" t="n">
-        <v>3647</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>1646</v>
       </c>
       <c r="C6" t="n">
-        <v>5004</v>
+        <v>4885</v>
       </c>
       <c r="D6" t="n">
-        <v>1482</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>820</v>
+        <v>952</v>
       </c>
       <c r="C7" t="n">
-        <v>3383</v>
+        <v>3597</v>
       </c>
       <c r="D7" t="n">
-        <v>763</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>379</v>
+        <v>459</v>
       </c>
       <c r="C8" t="n">
-        <v>1765</v>
+        <v>2129</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="C9" t="n">
-        <v>800</v>
+        <v>975</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7639</v>
+        <v>7727</v>
       </c>
       <c r="C2" t="n">
-        <v>8475</v>
+        <v>10989</v>
       </c>
       <c r="D2" t="n">
-        <v>19946</v>
+        <v>16569</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4843</v>
+        <v>5178</v>
       </c>
       <c r="C3" t="n">
-        <v>8930</v>
+        <v>12172</v>
       </c>
       <c r="D3" t="n">
-        <v>15918</v>
+        <v>15766</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1908</v>
+        <v>2126</v>
       </c>
       <c r="C4" t="n">
-        <v>7901</v>
+        <v>8650</v>
       </c>
       <c r="D4" t="n">
-        <v>8073</v>
+        <v>7171</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1314</v>
+        <v>1520</v>
       </c>
       <c r="C5" t="n">
-        <v>4903</v>
+        <v>4787</v>
       </c>
       <c r="D5" t="n">
-        <v>2432</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>757</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>3315</v>
+        <v>3525</v>
       </c>
       <c r="D6" t="n">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>424</v>
       </c>
       <c r="C7" t="n">
-        <v>1729</v>
+        <v>2086</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="C8" t="n">
-        <v>784</v>
+        <v>955</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4715</v>
+        <v>4798</v>
       </c>
       <c r="C2" t="n">
-        <v>3767</v>
+        <v>5423</v>
       </c>
       <c r="D2" t="n">
-        <v>13875</v>
+        <v>11785</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5167</v>
+        <v>5366</v>
       </c>
       <c r="C3" t="n">
-        <v>7915</v>
+        <v>10588</v>
       </c>
       <c r="D3" t="n">
-        <v>15701</v>
+        <v>15118</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2622</v>
+        <v>2832</v>
       </c>
       <c r="C4" t="n">
-        <v>8514</v>
+        <v>10391</v>
       </c>
       <c r="D4" t="n">
-        <v>9034</v>
+        <v>8328</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1462</v>
+        <v>1670</v>
       </c>
       <c r="C5" t="n">
-        <v>6198</v>
+        <v>6437</v>
       </c>
       <c r="D5" t="n">
-        <v>3108</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>896</v>
+        <v>1027</v>
       </c>
       <c r="C6" t="n">
-        <v>4066</v>
+        <v>4118</v>
       </c>
       <c r="D6" t="n">
-        <v>921</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>327</v>
+        <v>397</v>
       </c>
       <c r="C7" t="n">
-        <v>2283</v>
+        <v>2635</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>1061</v>
+        <v>1257</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="D9" t="n">
         <v>256</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>162</v>
+      </c>
+      <c r="D11" t="n">
         <v>165</v>
-      </c>
-      <c r="D11" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4225</v>
+        <v>4758</v>
       </c>
       <c r="C2" t="n">
-        <v>7159</v>
+        <v>7155</v>
       </c>
       <c r="D2" t="n">
-        <v>21921</v>
+        <v>10382</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4181</v>
+        <v>4316</v>
       </c>
       <c r="C3" t="n">
-        <v>5260</v>
+        <v>7353</v>
       </c>
       <c r="D3" t="n">
-        <v>14397</v>
+        <v>13648</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3189</v>
+        <v>3348</v>
       </c>
       <c r="C4" t="n">
-        <v>8043</v>
+        <v>10267</v>
       </c>
       <c r="D4" t="n">
-        <v>9847</v>
+        <v>9182</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1726</v>
+        <v>1911</v>
       </c>
       <c r="C5" t="n">
-        <v>7218</v>
+        <v>8087</v>
       </c>
       <c r="D5" t="n">
-        <v>3923</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1035</v>
+        <v>1179</v>
       </c>
       <c r="C6" t="n">
-        <v>4968</v>
+        <v>5121</v>
       </c>
       <c r="D6" t="n">
-        <v>1223</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>482</v>
+        <v>561</v>
       </c>
       <c r="C7" t="n">
-        <v>3073</v>
+        <v>3244</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="C8" t="n">
-        <v>1561</v>
+        <v>1808</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>648</v>
+        <v>731</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2549</v>
+        <v>2909</v>
       </c>
       <c r="C2" t="n">
-        <v>3345</v>
+        <v>3487</v>
       </c>
       <c r="D2" t="n">
-        <v>15331</v>
+        <v>7265</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4045</v>
+        <v>4263</v>
       </c>
       <c r="C3" t="n">
-        <v>5738</v>
+        <v>7089</v>
       </c>
       <c r="D3" t="n">
-        <v>14857</v>
+        <v>13002</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3515</v>
+        <v>3682</v>
       </c>
       <c r="C4" t="n">
-        <v>7816</v>
+        <v>10143</v>
       </c>
       <c r="D4" t="n">
-        <v>10451</v>
+        <v>9763</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1795</v>
+        <v>2009</v>
       </c>
       <c r="C5" t="n">
-        <v>8496</v>
+        <v>9775</v>
       </c>
       <c r="D5" t="n">
-        <v>4143</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>866</v>
+        <v>975</v>
       </c>
       <c r="C6" t="n">
-        <v>5916</v>
+        <v>6058</v>
       </c>
       <c r="D6" t="n">
-        <v>1204</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>3073</v>
+        <v>3356</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1109</v>
+        <v>1230</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2927</v>
+        <v>3340</v>
       </c>
       <c r="C2" t="n">
-        <v>6009</v>
+        <v>2664</v>
       </c>
       <c r="D2" t="n">
-        <v>17979</v>
+        <v>14384</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2938</v>
+        <v>3182</v>
       </c>
       <c r="C3" t="n">
-        <v>4147</v>
+        <v>4945</v>
       </c>
       <c r="D3" t="n">
-        <v>14065</v>
+        <v>11414</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3290</v>
+        <v>3450</v>
       </c>
       <c r="C4" t="n">
-        <v>6750</v>
+        <v>8554</v>
       </c>
       <c r="D4" t="n">
-        <v>10810</v>
+        <v>9963</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2192</v>
+        <v>2366</v>
       </c>
       <c r="C5" t="n">
-        <v>8100</v>
+        <v>9824</v>
       </c>
       <c r="D5" t="n">
-        <v>4925</v>
+        <v>4478</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1098</v>
+        <v>1223</v>
       </c>
       <c r="C6" t="n">
-        <v>6985</v>
+        <v>7562</v>
       </c>
       <c r="D6" t="n">
-        <v>1583</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>4216</v>
+        <v>4453</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1853</v>
+        <v>1982</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" t="n">
         <v>59</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2239</v>
+        <v>2395</v>
       </c>
       <c r="C2" t="n">
-        <v>3145</v>
+        <v>2129</v>
       </c>
       <c r="D2" t="n">
-        <v>13965</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2571</v>
+        <v>2833</v>
       </c>
       <c r="C3" t="n">
-        <v>4424</v>
+        <v>3764</v>
       </c>
       <c r="D3" t="n">
-        <v>13904</v>
+        <v>11143</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2937</v>
+        <v>3081</v>
       </c>
       <c r="C4" t="n">
-        <v>5754</v>
+        <v>7154</v>
       </c>
       <c r="D4" t="n">
-        <v>10991</v>
+        <v>9936</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2399</v>
+        <v>2562</v>
       </c>
       <c r="C5" t="n">
-        <v>7763</v>
+        <v>9557</v>
       </c>
       <c r="D5" t="n">
-        <v>5444</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1281</v>
+        <v>1400</v>
       </c>
       <c r="C6" t="n">
-        <v>7612</v>
+        <v>8535</v>
       </c>
       <c r="D6" t="n">
-        <v>1899</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>5154</v>
+        <v>5457</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2389</v>
+        <v>2529</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="n">
         <v>36</v>
-      </c>
-      <c r="D14" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3446</v>
+        <v>4616</v>
       </c>
       <c r="C2" t="n">
-        <v>10835</v>
+        <v>2911</v>
       </c>
       <c r="D2" t="n">
-        <v>16480</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2068</v>
+        <v>2263</v>
       </c>
       <c r="C3" t="n">
-        <v>3485</v>
+        <v>2828</v>
       </c>
       <c r="D3" t="n">
-        <v>13021</v>
+        <v>10348</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2443</v>
+        <v>2605</v>
       </c>
       <c r="C4" t="n">
-        <v>5072</v>
+        <v>5638</v>
       </c>
       <c r="D4" t="n">
-        <v>11076</v>
+        <v>9796</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2355</v>
+        <v>2520</v>
       </c>
       <c r="C5" t="n">
-        <v>6791</v>
+        <v>8435</v>
       </c>
       <c r="D5" t="n">
-        <v>6024</v>
+        <v>5421</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1539</v>
+        <v>1630</v>
       </c>
       <c r="C6" t="n">
-        <v>7606</v>
+        <v>8839</v>
       </c>
       <c r="D6" t="n">
-        <v>2317</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>534</v>
+        <v>578</v>
       </c>
       <c r="C7" t="n">
-        <v>6117</v>
+        <v>6540</v>
       </c>
       <c r="D7" t="n">
-        <v>846</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>3336</v>
+        <v>3528</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1202</v>
+        <v>1212</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6045</v>
+        <v>9640</v>
       </c>
       <c r="C2" t="n">
-        <v>5351</v>
+        <v>7132</v>
       </c>
       <c r="D2" t="n">
-        <v>5893</v>
+        <v>8327</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2493</v>
+        <v>3373</v>
       </c>
       <c r="C2" t="n">
-        <v>6240</v>
+        <v>1700</v>
       </c>
       <c r="D2" t="n">
-        <v>12261</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2828</v>
+        <v>3126</v>
       </c>
       <c r="C3" t="n">
-        <v>5438</v>
+        <v>3153</v>
       </c>
       <c r="D3" t="n">
-        <v>14167</v>
+        <v>11169</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3422</v>
+        <v>3659</v>
       </c>
       <c r="C4" t="n">
-        <v>7355</v>
+        <v>8355</v>
       </c>
       <c r="D4" t="n">
-        <v>11334</v>
+        <v>9952</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1465</v>
+        <v>1529</v>
       </c>
       <c r="C5" t="n">
-        <v>10405</v>
+        <v>12447</v>
       </c>
       <c r="D5" t="n">
-        <v>5472</v>
+        <v>4942</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="C6" t="n">
-        <v>7410</v>
+        <v>7968</v>
       </c>
       <c r="D6" t="n">
-        <v>1856</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>3269</v>
+        <v>3457</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1177</v>
+        <v>1187</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7507</v>
+        <v>8568</v>
       </c>
       <c r="C2" t="n">
-        <v>7684</v>
+        <v>9362</v>
       </c>
       <c r="D2" t="n">
-        <v>13328</v>
+        <v>11565</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2568</v>
+        <v>4092</v>
       </c>
       <c r="C3" t="n">
-        <v>2739</v>
+        <v>3594</v>
       </c>
       <c r="D3" t="n">
-        <v>1676</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5096</v>
+        <v>5484</v>
       </c>
       <c r="C2" t="n">
-        <v>6802</v>
+        <v>11883</v>
       </c>
       <c r="D2" t="n">
-        <v>17506</v>
+        <v>14593</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4134</v>
+        <v>5204</v>
       </c>
       <c r="C3" t="n">
-        <v>4836</v>
+        <v>5914</v>
       </c>
       <c r="D3" t="n">
-        <v>3510</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1149</v>
+        <v>1812</v>
       </c>
       <c r="C4" t="n">
-        <v>1647</v>
+        <v>2150</v>
       </c>
       <c r="D4" t="n">
-        <v>1519</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4934</v>
+        <v>5859</v>
       </c>
       <c r="C2" t="n">
-        <v>7474</v>
+        <v>9214</v>
       </c>
       <c r="D2" t="n">
-        <v>25567</v>
+        <v>16116</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3793</v>
+        <v>4410</v>
       </c>
       <c r="C3" t="n">
-        <v>5113</v>
+        <v>7898</v>
       </c>
       <c r="D3" t="n">
-        <v>5496</v>
+        <v>5013</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2234</v>
+        <v>2990</v>
       </c>
       <c r="C4" t="n">
-        <v>3418</v>
+        <v>4180</v>
       </c>
       <c r="D4" t="n">
-        <v>1855</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>532</v>
+        <v>787</v>
       </c>
       <c r="C5" t="n">
-        <v>994</v>
+        <v>1271</v>
       </c>
       <c r="D5" t="n">
-        <v>1199</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5937</v>
+        <v>6592</v>
       </c>
       <c r="C2" t="n">
-        <v>13265</v>
+        <v>6488</v>
       </c>
       <c r="D2" t="n">
-        <v>23827</v>
+        <v>23395</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3567</v>
+        <v>4185</v>
       </c>
       <c r="C3" t="n">
-        <v>5508</v>
+        <v>7466</v>
       </c>
       <c r="D3" t="n">
-        <v>8159</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2565</v>
+        <v>3129</v>
       </c>
       <c r="C4" t="n">
-        <v>4258</v>
+        <v>6016</v>
       </c>
       <c r="D4" t="n">
-        <v>2462</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1131</v>
+        <v>1560</v>
       </c>
       <c r="C5" t="n">
-        <v>2220</v>
+        <v>2752</v>
       </c>
       <c r="D5" t="n">
-        <v>1264</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>295</v>
+        <v>392</v>
       </c>
       <c r="C6" t="n">
-        <v>651</v>
+        <v>783</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6030</v>
+        <v>7702</v>
       </c>
       <c r="C2" t="n">
-        <v>10469</v>
+        <v>7666</v>
       </c>
       <c r="D2" t="n">
-        <v>30370</v>
+        <v>24281</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3426</v>
+        <v>3868</v>
       </c>
       <c r="C3" t="n">
-        <v>7759</v>
+        <v>5719</v>
       </c>
       <c r="D3" t="n">
-        <v>9376</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1892</v>
+        <v>2245</v>
       </c>
       <c r="C4" t="n">
-        <v>4052</v>
+        <v>5564</v>
       </c>
       <c r="D4" t="n">
-        <v>2990</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>968</v>
+        <v>1229</v>
       </c>
       <c r="C5" t="n">
-        <v>2379</v>
+        <v>3205</v>
       </c>
       <c r="D5" t="n">
-        <v>1150</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>334</v>
+        <v>450</v>
       </c>
       <c r="C6" t="n">
-        <v>971</v>
+        <v>1182</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5601</v>
+        <v>5785</v>
       </c>
       <c r="C2" t="n">
-        <v>5928</v>
+        <v>11751</v>
       </c>
       <c r="D2" t="n">
-        <v>28619</v>
+        <v>27876</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3928</v>
+        <v>4785</v>
       </c>
       <c r="C3" t="n">
-        <v>8032</v>
+        <v>5888</v>
       </c>
       <c r="D3" t="n">
-        <v>12212</v>
+        <v>10137</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2336</v>
+        <v>2670</v>
       </c>
       <c r="C4" t="n">
-        <v>6209</v>
+        <v>5540</v>
       </c>
       <c r="D4" t="n">
-        <v>4157</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1278</v>
+        <v>1535</v>
       </c>
       <c r="C5" t="n">
-        <v>3309</v>
+        <v>4466</v>
       </c>
       <c r="D5" t="n">
-        <v>1485</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>598</v>
+        <v>776</v>
       </c>
       <c r="C6" t="n">
-        <v>1756</v>
+        <v>2313</v>
       </c>
       <c r="D6" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>679</v>
+        <v>816</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5918</v>
+        <v>5514</v>
       </c>
       <c r="C2" t="n">
-        <v>4120</v>
+        <v>7653</v>
       </c>
       <c r="D2" t="n">
-        <v>24099</v>
+        <v>28309</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3902</v>
+        <v>4341</v>
       </c>
       <c r="C3" t="n">
-        <v>5989</v>
+        <v>7789</v>
       </c>
       <c r="D3" t="n">
-        <v>13957</v>
+        <v>12119</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2694</v>
+        <v>3185</v>
       </c>
       <c r="C4" t="n">
-        <v>7035</v>
+        <v>5562</v>
       </c>
       <c r="D4" t="n">
-        <v>5577</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1573</v>
+        <v>1826</v>
       </c>
       <c r="C5" t="n">
-        <v>4827</v>
+        <v>4950</v>
       </c>
       <c r="D5" t="n">
-        <v>1912</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>852</v>
+        <v>1046</v>
       </c>
       <c r="C6" t="n">
-        <v>2555</v>
+        <v>3403</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>1238</v>
+        <v>1578</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>473</v>
+        <v>546</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_48_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6437</v>
+        <v>7005</v>
       </c>
       <c r="C2" t="n">
-        <v>5421</v>
+        <v>6346</v>
       </c>
       <c r="D2" t="n">
-        <v>26804</v>
+        <v>18940</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4012</v>
+        <v>3618</v>
       </c>
       <c r="C3" t="n">
-        <v>6772</v>
+        <v>5583</v>
       </c>
       <c r="D3" t="n">
-        <v>13616</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3201</v>
+        <v>3128</v>
       </c>
       <c r="C4" t="n">
-        <v>6504</v>
+        <v>3454</v>
       </c>
       <c r="D4" t="n">
-        <v>5833</v>
+        <v>5621</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2135</v>
+        <v>1956</v>
       </c>
       <c r="C5" t="n">
-        <v>5146</v>
+        <v>3494</v>
       </c>
       <c r="D5" t="n">
-        <v>2176</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1271</v>
+        <v>1048</v>
       </c>
       <c r="C6" t="n">
-        <v>4062</v>
+        <v>2658</v>
       </c>
       <c r="D6" t="n">
-        <v>1037</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>640</v>
+        <v>474</v>
       </c>
       <c r="C7" t="n">
-        <v>2435</v>
+        <v>1562</v>
       </c>
       <c r="D7" t="n">
-        <v>634</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>236</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>1005</v>
+        <v>772</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7285</v>
+        <v>7017</v>
       </c>
       <c r="C2" t="n">
-        <v>15958</v>
+        <v>5478</v>
       </c>
       <c r="D2" t="n">
-        <v>24506</v>
+        <v>19909</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4110</v>
+        <v>4222</v>
       </c>
       <c r="C3" t="n">
-        <v>5462</v>
+        <v>5212</v>
       </c>
       <c r="D3" t="n">
-        <v>14410</v>
+        <v>11111</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3058</v>
+        <v>2871</v>
       </c>
       <c r="C4" t="n">
-        <v>6492</v>
+        <v>4411</v>
       </c>
       <c r="D4" t="n">
-        <v>6795</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2279</v>
+        <v>2185</v>
       </c>
       <c r="C5" t="n">
-        <v>5589</v>
+        <v>3401</v>
       </c>
       <c r="D5" t="n">
-        <v>2671</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1481</v>
+        <v>1331</v>
       </c>
       <c r="C6" t="n">
-        <v>4492</v>
+        <v>2998</v>
       </c>
       <c r="D6" t="n">
-        <v>1177</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>807</v>
+        <v>649</v>
       </c>
       <c r="C7" t="n">
-        <v>3095</v>
+        <v>2076</v>
       </c>
       <c r="D7" t="n">
-        <v>686</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>353</v>
+        <v>264</v>
       </c>
       <c r="C8" t="n">
-        <v>1583</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>630</v>
+        <v>530</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8353</v>
+        <v>9336</v>
       </c>
       <c r="C2" t="n">
-        <v>15610</v>
+        <v>8249</v>
       </c>
       <c r="D2" t="n">
-        <v>19830</v>
+        <v>25414</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4339</v>
+        <v>4403</v>
       </c>
       <c r="C3" t="n">
-        <v>8478</v>
+        <v>4705</v>
       </c>
       <c r="D3" t="n">
-        <v>14699</v>
+        <v>11508</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2954</v>
+        <v>2930</v>
       </c>
       <c r="C4" t="n">
-        <v>5869</v>
+        <v>4646</v>
       </c>
       <c r="D4" t="n">
-        <v>7684</v>
+        <v>6802</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2301</v>
+        <v>2205</v>
       </c>
       <c r="C5" t="n">
-        <v>5783</v>
+        <v>3785</v>
       </c>
       <c r="D5" t="n">
-        <v>3118</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1646</v>
+        <v>1554</v>
       </c>
       <c r="C6" t="n">
-        <v>4885</v>
+        <v>3114</v>
       </c>
       <c r="D6" t="n">
-        <v>1362</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>952</v>
+        <v>832</v>
       </c>
       <c r="C7" t="n">
-        <v>3597</v>
+        <v>2472</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>802</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>459</v>
+        <v>370</v>
       </c>
       <c r="C8" t="n">
-        <v>2129</v>
+        <v>1506</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C9" t="n">
-        <v>975</v>
+        <v>764</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7727</v>
+        <v>8342</v>
       </c>
       <c r="C2" t="n">
-        <v>10989</v>
+        <v>5411</v>
       </c>
       <c r="D2" t="n">
-        <v>16569</v>
+        <v>20569</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5178</v>
+        <v>5384</v>
       </c>
       <c r="C3" t="n">
-        <v>12172</v>
+        <v>7488</v>
       </c>
       <c r="D3" t="n">
-        <v>15766</v>
+        <v>12833</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2126</v>
+        <v>2037</v>
       </c>
       <c r="C4" t="n">
-        <v>8650</v>
+        <v>6309</v>
       </c>
       <c r="D4" t="n">
-        <v>7171</v>
+        <v>6792</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1520</v>
+        <v>1435</v>
       </c>
       <c r="C5" t="n">
-        <v>4787</v>
+        <v>3051</v>
       </c>
       <c r="D5" t="n">
-        <v>2172</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>768</v>
       </c>
       <c r="C6" t="n">
-        <v>3525</v>
+        <v>2422</v>
       </c>
       <c r="D6" t="n">
-        <v>719</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>2086</v>
+        <v>1475</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>955</v>
+        <v>748</v>
       </c>
       <c r="D8" t="n">
-        <v>318</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4798</v>
+        <v>4987</v>
       </c>
       <c r="C2" t="n">
-        <v>5423</v>
+        <v>2760</v>
       </c>
       <c r="D2" t="n">
-        <v>11785</v>
+        <v>14659</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5366</v>
+        <v>5738</v>
       </c>
       <c r="C3" t="n">
-        <v>10588</v>
+        <v>5859</v>
       </c>
       <c r="D3" t="n">
-        <v>15118</v>
+        <v>13310</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2832</v>
+        <v>2918</v>
       </c>
       <c r="C4" t="n">
-        <v>10391</v>
+        <v>6997</v>
       </c>
       <c r="D4" t="n">
-        <v>8328</v>
+        <v>7578</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1670</v>
+        <v>1595</v>
       </c>
       <c r="C5" t="n">
-        <v>6437</v>
+        <v>4541</v>
       </c>
       <c r="D5" t="n">
-        <v>2723</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1027</v>
+        <v>936</v>
       </c>
       <c r="C6" t="n">
-        <v>4118</v>
+        <v>2774</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>325</v>
       </c>
       <c r="C7" t="n">
-        <v>2635</v>
+        <v>1882</v>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1257</v>
+        <v>992</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4758</v>
+        <v>6108</v>
       </c>
       <c r="C2" t="n">
-        <v>7155</v>
+        <v>6652</v>
       </c>
       <c r="D2" t="n">
-        <v>10382</v>
+        <v>17637</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4316</v>
+        <v>4533</v>
       </c>
       <c r="C3" t="n">
-        <v>7353</v>
+        <v>3779</v>
       </c>
       <c r="D3" t="n">
-        <v>13648</v>
+        <v>12588</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3348</v>
+        <v>3617</v>
       </c>
       <c r="C4" t="n">
-        <v>10267</v>
+        <v>6261</v>
       </c>
       <c r="D4" t="n">
-        <v>9182</v>
+        <v>8338</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1911</v>
+        <v>1933</v>
       </c>
       <c r="C5" t="n">
-        <v>8087</v>
+        <v>5716</v>
       </c>
       <c r="D5" t="n">
-        <v>3501</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1179</v>
+        <v>1122</v>
       </c>
       <c r="C6" t="n">
-        <v>5121</v>
+        <v>3576</v>
       </c>
       <c r="D6" t="n">
-        <v>1114</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>561</v>
+        <v>509</v>
       </c>
       <c r="C7" t="n">
-        <v>3244</v>
+        <v>2310</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>1808</v>
+        <v>1385</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>731</v>
+        <v>661</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2909</v>
+        <v>3529</v>
       </c>
       <c r="C2" t="n">
-        <v>3487</v>
+        <v>2966</v>
       </c>
       <c r="D2" t="n">
-        <v>7265</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4263</v>
+        <v>4758</v>
       </c>
       <c r="C3" t="n">
-        <v>7089</v>
+        <v>4680</v>
       </c>
       <c r="D3" t="n">
-        <v>13002</v>
+        <v>12851</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3682</v>
+        <v>4021</v>
       </c>
       <c r="C4" t="n">
-        <v>10143</v>
+        <v>5850</v>
       </c>
       <c r="D4" t="n">
-        <v>9763</v>
+        <v>8892</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>9775</v>
+        <v>6656</v>
       </c>
       <c r="D5" t="n">
-        <v>3722</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>975</v>
+        <v>947</v>
       </c>
       <c r="C6" t="n">
-        <v>6058</v>
+        <v>4517</v>
       </c>
       <c r="D6" t="n">
-        <v>1094</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>3356</v>
+        <v>2480</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1230</v>
+        <v>1109</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3340</v>
+        <v>4029</v>
       </c>
       <c r="C2" t="n">
-        <v>2664</v>
+        <v>5923</v>
       </c>
       <c r="D2" t="n">
-        <v>14384</v>
+        <v>18004</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3182</v>
+        <v>3565</v>
       </c>
       <c r="C3" t="n">
-        <v>4945</v>
+        <v>3414</v>
       </c>
       <c r="D3" t="n">
-        <v>11414</v>
+        <v>11994</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3450</v>
+        <v>3826</v>
       </c>
       <c r="C4" t="n">
-        <v>8554</v>
+        <v>5200</v>
       </c>
       <c r="D4" t="n">
-        <v>9963</v>
+        <v>9267</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2366</v>
+        <v>2536</v>
       </c>
       <c r="C5" t="n">
-        <v>9824</v>
+        <v>6202</v>
       </c>
       <c r="D5" t="n">
-        <v>4478</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1223</v>
+        <v>1257</v>
       </c>
       <c r="C6" t="n">
-        <v>7562</v>
+        <v>5462</v>
       </c>
       <c r="D6" t="n">
-        <v>1443</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>4453</v>
+        <v>3386</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1982</v>
+        <v>1654</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2395</v>
+        <v>3055</v>
       </c>
       <c r="C2" t="n">
-        <v>2129</v>
+        <v>3927</v>
       </c>
       <c r="D2" t="n">
-        <v>10261</v>
+        <v>12491</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2833</v>
+        <v>3258</v>
       </c>
       <c r="C3" t="n">
-        <v>3764</v>
+        <v>4077</v>
       </c>
       <c r="D3" t="n">
-        <v>11143</v>
+        <v>12091</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>3416</v>
       </c>
       <c r="C4" t="n">
-        <v>7154</v>
+        <v>4470</v>
       </c>
       <c r="D4" t="n">
-        <v>9936</v>
+        <v>9555</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2562</v>
+        <v>2806</v>
       </c>
       <c r="C5" t="n">
-        <v>9557</v>
+        <v>5926</v>
       </c>
       <c r="D5" t="n">
-        <v>5007</v>
+        <v>5035</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1400</v>
+        <v>1498</v>
       </c>
       <c r="C6" t="n">
-        <v>8535</v>
+        <v>5931</v>
       </c>
       <c r="D6" t="n">
-        <v>1687</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="C7" t="n">
-        <v>5457</v>
+        <v>4166</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2529</v>
+        <v>2116</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>638</v>
+        <v>720</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4616</v>
+        <v>5721</v>
       </c>
       <c r="C2" t="n">
-        <v>2911</v>
+        <v>6198</v>
       </c>
       <c r="D2" t="n">
-        <v>8631</v>
+        <v>23510</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2263</v>
+        <v>2674</v>
       </c>
       <c r="C3" t="n">
-        <v>2828</v>
+        <v>3550</v>
       </c>
       <c r="D3" t="n">
-        <v>10348</v>
+        <v>11349</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2605</v>
+        <v>2917</v>
       </c>
       <c r="C4" t="n">
-        <v>5638</v>
+        <v>4199</v>
       </c>
       <c r="D4" t="n">
-        <v>9796</v>
+        <v>9654</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2520</v>
+        <v>2784</v>
       </c>
       <c r="C5" t="n">
-        <v>8435</v>
+        <v>5173</v>
       </c>
       <c r="D5" t="n">
-        <v>5421</v>
+        <v>5532</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1630</v>
+        <v>1824</v>
       </c>
       <c r="C6" t="n">
-        <v>8839</v>
+        <v>5875</v>
       </c>
       <c r="D6" t="n">
-        <v>2079</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>578</v>
+        <v>662</v>
       </c>
       <c r="C7" t="n">
-        <v>6540</v>
+        <v>4914</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>902</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>3528</v>
+        <v>2878</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9640</v>
+        <v>4144</v>
       </c>
       <c r="C2" t="n">
-        <v>7132</v>
+        <v>5883</v>
       </c>
       <c r="D2" t="n">
-        <v>8327</v>
+        <v>5497</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3373</v>
+        <v>4001</v>
       </c>
       <c r="C2" t="n">
-        <v>1700</v>
+        <v>3421</v>
       </c>
       <c r="D2" t="n">
-        <v>6421</v>
+        <v>17304</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>3767</v>
       </c>
       <c r="C3" t="n">
-        <v>3153</v>
+        <v>4502</v>
       </c>
       <c r="D3" t="n">
-        <v>11169</v>
+        <v>12955</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3659</v>
+        <v>4034</v>
       </c>
       <c r="C4" t="n">
-        <v>8355</v>
+        <v>5963</v>
       </c>
       <c r="D4" t="n">
-        <v>9952</v>
+        <v>9986</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1529</v>
+        <v>1813</v>
       </c>
       <c r="C5" t="n">
-        <v>12447</v>
+        <v>7967</v>
       </c>
       <c r="D5" t="n">
-        <v>4942</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>534</v>
+        <v>611</v>
       </c>
       <c r="C6" t="n">
-        <v>7968</v>
+        <v>6082</v>
       </c>
       <c r="D6" t="n">
-        <v>1666</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>3457</v>
+        <v>2820</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8568</v>
+        <v>6647</v>
       </c>
       <c r="C2" t="n">
-        <v>9362</v>
+        <v>4668</v>
       </c>
       <c r="D2" t="n">
-        <v>11565</v>
+        <v>20978</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4092</v>
+        <v>1762</v>
       </c>
       <c r="C3" t="n">
-        <v>3594</v>
+        <v>3012</v>
       </c>
       <c r="D3" t="n">
-        <v>2038</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5484</v>
+        <v>5284</v>
       </c>
       <c r="C2" t="n">
-        <v>11883</v>
+        <v>4974</v>
       </c>
       <c r="D2" t="n">
-        <v>14593</v>
+        <v>18363</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5204</v>
+        <v>3447</v>
       </c>
       <c r="C3" t="n">
-        <v>5914</v>
+        <v>3443</v>
       </c>
       <c r="D3" t="n">
-        <v>3488</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1812</v>
+        <v>799</v>
       </c>
       <c r="C4" t="n">
-        <v>2150</v>
+        <v>1807</v>
       </c>
       <c r="D4" t="n">
-        <v>1592</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5859</v>
+        <v>5908</v>
       </c>
       <c r="C2" t="n">
-        <v>9214</v>
+        <v>6118</v>
       </c>
       <c r="D2" t="n">
-        <v>16116</v>
+        <v>18914</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4410</v>
+        <v>3569</v>
       </c>
       <c r="C3" t="n">
-        <v>7898</v>
+        <v>3702</v>
       </c>
       <c r="D3" t="n">
-        <v>5013</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2990</v>
+        <v>1793</v>
       </c>
       <c r="C4" t="n">
-        <v>4180</v>
+        <v>2696</v>
       </c>
       <c r="D4" t="n">
-        <v>1907</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>787</v>
+        <v>389</v>
       </c>
       <c r="C5" t="n">
-        <v>1271</v>
+        <v>1081</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6592</v>
+        <v>5467</v>
       </c>
       <c r="C2" t="n">
-        <v>6488</v>
+        <v>6482</v>
       </c>
       <c r="D2" t="n">
-        <v>23395</v>
+        <v>17489</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4185</v>
+        <v>3833</v>
       </c>
       <c r="C3" t="n">
-        <v>7466</v>
+        <v>4317</v>
       </c>
       <c r="D3" t="n">
-        <v>6347</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3129</v>
+        <v>2254</v>
       </c>
       <c r="C4" t="n">
-        <v>6016</v>
+        <v>3190</v>
       </c>
       <c r="D4" t="n">
-        <v>2415</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1560</v>
+        <v>903</v>
       </c>
       <c r="C5" t="n">
-        <v>2752</v>
+        <v>1911</v>
       </c>
       <c r="D5" t="n">
-        <v>1290</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>392</v>
+        <v>235</v>
       </c>
       <c r="C6" t="n">
-        <v>783</v>
+        <v>692</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7702</v>
+        <v>7460</v>
       </c>
       <c r="C2" t="n">
-        <v>7666</v>
+        <v>4628</v>
       </c>
       <c r="D2" t="n">
-        <v>24281</v>
+        <v>14966</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3868</v>
+        <v>3383</v>
       </c>
       <c r="C3" t="n">
-        <v>5719</v>
+        <v>4457</v>
       </c>
       <c r="D3" t="n">
-        <v>7988</v>
+        <v>8346</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245</v>
+        <v>1901</v>
       </c>
       <c r="C4" t="n">
-        <v>5564</v>
+        <v>3134</v>
       </c>
       <c r="D4" t="n">
-        <v>2667</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1229</v>
+        <v>817</v>
       </c>
       <c r="C5" t="n">
-        <v>3205</v>
+        <v>1877</v>
       </c>
       <c r="D5" t="n">
-        <v>1160</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>1182</v>
+        <v>888</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5785</v>
+        <v>5921</v>
       </c>
       <c r="C2" t="n">
-        <v>11751</v>
+        <v>3885</v>
       </c>
       <c r="D2" t="n">
-        <v>27876</v>
+        <v>16561</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4785</v>
+        <v>4548</v>
       </c>
       <c r="C3" t="n">
-        <v>5888</v>
+        <v>3904</v>
       </c>
       <c r="D3" t="n">
-        <v>10137</v>
+        <v>8883</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2670</v>
+        <v>2333</v>
       </c>
       <c r="C4" t="n">
-        <v>5540</v>
+        <v>3894</v>
       </c>
       <c r="D4" t="n">
-        <v>3658</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1535</v>
+        <v>1212</v>
       </c>
       <c r="C5" t="n">
-        <v>4466</v>
+        <v>2598</v>
       </c>
       <c r="D5" t="n">
-        <v>1402</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>776</v>
+        <v>512</v>
       </c>
       <c r="C6" t="n">
-        <v>2313</v>
+        <v>1455</v>
       </c>
       <c r="D6" t="n">
-        <v>830</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>816</v>
+        <v>654</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5514</v>
+        <v>4442</v>
       </c>
       <c r="C2" t="n">
-        <v>7653</v>
+        <v>9297</v>
       </c>
       <c r="D2" t="n">
-        <v>28309</v>
+        <v>21373</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4341</v>
+        <v>4314</v>
       </c>
       <c r="C3" t="n">
-        <v>7789</v>
+        <v>3357</v>
       </c>
       <c r="D3" t="n">
-        <v>12119</v>
+        <v>9519</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3185</v>
+        <v>2989</v>
       </c>
       <c r="C4" t="n">
-        <v>5562</v>
+        <v>3818</v>
       </c>
       <c r="D4" t="n">
-        <v>4693</v>
+        <v>4997</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1826</v>
+        <v>1567</v>
       </c>
       <c r="C5" t="n">
-        <v>4950</v>
+        <v>3278</v>
       </c>
       <c r="D5" t="n">
-        <v>1770</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1046</v>
+        <v>781</v>
       </c>
       <c r="C6" t="n">
-        <v>3403</v>
+        <v>2063</v>
       </c>
       <c r="D6" t="n">
-        <v>909</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>301</v>
       </c>
       <c r="C7" t="n">
-        <v>1578</v>
+        <v>1085</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>546</v>
+        <v>473</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_48_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7005</v>
+        <v>1717</v>
       </c>
       <c r="C2" t="n">
-        <v>6346</v>
+        <v>2801</v>
       </c>
       <c r="D2" t="n">
-        <v>18940</v>
+        <v>12406</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3618</v>
+        <v>2826</v>
       </c>
       <c r="C3" t="n">
-        <v>5583</v>
+        <v>5300</v>
       </c>
       <c r="D3" t="n">
-        <v>10650</v>
+        <v>12779</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3128</v>
+        <v>1841</v>
       </c>
       <c r="C4" t="n">
-        <v>3454</v>
+        <v>6140</v>
       </c>
       <c r="D4" t="n">
-        <v>5621</v>
+        <v>5792</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1956</v>
+        <v>1019</v>
       </c>
       <c r="C5" t="n">
-        <v>3494</v>
+        <v>3607</v>
       </c>
       <c r="D5" t="n">
-        <v>2518</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1048</v>
+        <v>409</v>
       </c>
       <c r="C6" t="n">
-        <v>2658</v>
+        <v>1341</v>
       </c>
       <c r="D6" t="n">
-        <v>1137</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>474</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>1562</v>
+        <v>508</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>772</v>
+        <v>331</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7017</v>
+        <v>1681</v>
       </c>
       <c r="C2" t="n">
-        <v>5478</v>
+        <v>5710</v>
       </c>
       <c r="D2" t="n">
-        <v>19909</v>
+        <v>15309</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4222</v>
+        <v>1925</v>
       </c>
       <c r="C3" t="n">
-        <v>5212</v>
+        <v>3408</v>
       </c>
       <c r="D3" t="n">
-        <v>11111</v>
+        <v>11799</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2871</v>
+        <v>2018</v>
       </c>
       <c r="C4" t="n">
-        <v>4411</v>
+        <v>5595</v>
       </c>
       <c r="D4" t="n">
-        <v>6319</v>
+        <v>6957</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2185</v>
+        <v>1251</v>
       </c>
       <c r="C5" t="n">
-        <v>3401</v>
+        <v>4928</v>
       </c>
       <c r="D5" t="n">
-        <v>2923</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1331</v>
+        <v>629</v>
       </c>
       <c r="C6" t="n">
-        <v>2998</v>
+        <v>2479</v>
       </c>
       <c r="D6" t="n">
-        <v>1346</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>649</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
-        <v>2076</v>
+        <v>934</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>415</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>530</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
+        <v>248</v>
+      </c>
+      <c r="D10" t="n">
         <v>273</v>
-      </c>
-      <c r="D10" t="n">
-        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9336</v>
+        <v>870</v>
       </c>
       <c r="C2" t="n">
-        <v>8249</v>
+        <v>2261</v>
       </c>
       <c r="D2" t="n">
-        <v>25414</v>
+        <v>10327</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4403</v>
+        <v>1779</v>
       </c>
       <c r="C3" t="n">
-        <v>4705</v>
+        <v>4194</v>
       </c>
       <c r="D3" t="n">
-        <v>11508</v>
+        <v>11927</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2930</v>
+        <v>2225</v>
       </c>
       <c r="C4" t="n">
-        <v>4646</v>
+        <v>5166</v>
       </c>
       <c r="D4" t="n">
-        <v>6802</v>
+        <v>7637</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2205</v>
+        <v>1284</v>
       </c>
       <c r="C5" t="n">
-        <v>3785</v>
+        <v>5727</v>
       </c>
       <c r="D5" t="n">
-        <v>3355</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1554</v>
+        <v>485</v>
       </c>
       <c r="C6" t="n">
-        <v>3114</v>
+        <v>3273</v>
       </c>
       <c r="D6" t="n">
-        <v>1542</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>832</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>2472</v>
+        <v>938</v>
       </c>
       <c r="D7" t="n">
-        <v>802</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>370</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1506</v>
+        <v>462</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>764</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>373</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8342</v>
+        <v>1064</v>
       </c>
       <c r="C2" t="n">
-        <v>5411</v>
+        <v>4119</v>
       </c>
       <c r="D2" t="n">
-        <v>20569</v>
+        <v>9182</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5384</v>
+        <v>1152</v>
       </c>
       <c r="C3" t="n">
-        <v>7488</v>
+        <v>2780</v>
       </c>
       <c r="D3" t="n">
-        <v>12833</v>
+        <v>10926</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2037</v>
+        <v>1796</v>
       </c>
       <c r="C4" t="n">
-        <v>6309</v>
+        <v>4576</v>
       </c>
       <c r="D4" t="n">
-        <v>6792</v>
+        <v>8187</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1435</v>
+        <v>1531</v>
       </c>
       <c r="C5" t="n">
-        <v>3051</v>
+        <v>5372</v>
       </c>
       <c r="D5" t="n">
-        <v>2445</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>768</v>
+        <v>751</v>
       </c>
       <c r="C6" t="n">
-        <v>2422</v>
+        <v>4503</v>
       </c>
       <c r="D6" t="n">
-        <v>785</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>201</v>
       </c>
       <c r="C7" t="n">
-        <v>1475</v>
+        <v>2031</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>748</v>
+        <v>671</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4987</v>
+        <v>582</v>
       </c>
       <c r="C2" t="n">
-        <v>2760</v>
+        <v>2229</v>
       </c>
       <c r="D2" t="n">
-        <v>14659</v>
+        <v>7047</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5738</v>
+        <v>975</v>
       </c>
       <c r="C3" t="n">
-        <v>5859</v>
+        <v>3054</v>
       </c>
       <c r="D3" t="n">
-        <v>13310</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2918</v>
+        <v>1449</v>
       </c>
       <c r="C4" t="n">
-        <v>6997</v>
+        <v>3733</v>
       </c>
       <c r="D4" t="n">
-        <v>7578</v>
+        <v>8542</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="C5" t="n">
-        <v>4541</v>
+        <v>5115</v>
       </c>
       <c r="D5" t="n">
-        <v>3001</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>936</v>
+        <v>917</v>
       </c>
       <c r="C6" t="n">
-        <v>2774</v>
+        <v>5063</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>241</v>
       </c>
       <c r="C7" t="n">
-        <v>1882</v>
+        <v>2944</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>1043</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6108</v>
+        <v>740</v>
       </c>
       <c r="C2" t="n">
-        <v>6652</v>
+        <v>11384</v>
       </c>
       <c r="D2" t="n">
-        <v>17637</v>
+        <v>7037</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4533</v>
+        <v>678</v>
       </c>
       <c r="C3" t="n">
-        <v>3779</v>
+        <v>2340</v>
       </c>
       <c r="D3" t="n">
-        <v>12588</v>
+        <v>8908</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3617</v>
+        <v>1085</v>
       </c>
       <c r="C4" t="n">
-        <v>6261</v>
+        <v>3309</v>
       </c>
       <c r="D4" t="n">
-        <v>8338</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1933</v>
+        <v>1416</v>
       </c>
       <c r="C5" t="n">
-        <v>5716</v>
+        <v>4381</v>
       </c>
       <c r="D5" t="n">
-        <v>3656</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1122</v>
+        <v>1108</v>
       </c>
       <c r="C6" t="n">
-        <v>3576</v>
+        <v>5036</v>
       </c>
       <c r="D6" t="n">
-        <v>1278</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>509</v>
+        <v>450</v>
       </c>
       <c r="C7" t="n">
-        <v>2310</v>
+        <v>3926</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>1385</v>
+        <v>1853</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3529</v>
+        <v>485</v>
       </c>
       <c r="C2" t="n">
-        <v>2966</v>
+        <v>5646</v>
       </c>
       <c r="D2" t="n">
-        <v>12188</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4758</v>
+        <v>961</v>
       </c>
       <c r="C3" t="n">
-        <v>4680</v>
+        <v>5257</v>
       </c>
       <c r="D3" t="n">
-        <v>12851</v>
+        <v>9413</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4021</v>
+        <v>1824</v>
       </c>
       <c r="C4" t="n">
-        <v>5850</v>
+        <v>4635</v>
       </c>
       <c r="D4" t="n">
-        <v>8892</v>
+        <v>8969</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>1154</v>
       </c>
       <c r="C5" t="n">
-        <v>6656</v>
+        <v>6749</v>
       </c>
       <c r="D5" t="n">
-        <v>3955</v>
+        <v>4507</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>415</v>
       </c>
       <c r="C6" t="n">
-        <v>4517</v>
+        <v>5229</v>
       </c>
       <c r="D6" t="n">
-        <v>1264</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>2480</v>
+        <v>1815</v>
       </c>
       <c r="D7" t="n">
-        <v>590</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1109</v>
+        <v>661</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4029</v>
+        <v>373</v>
       </c>
       <c r="C2" t="n">
-        <v>5923</v>
+        <v>2192</v>
       </c>
       <c r="D2" t="n">
-        <v>18004</v>
+        <v>5172</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3565</v>
+        <v>635</v>
       </c>
       <c r="C3" t="n">
-        <v>3414</v>
+        <v>4834</v>
       </c>
       <c r="D3" t="n">
-        <v>11994</v>
+        <v>8055</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3826</v>
+        <v>1187</v>
       </c>
       <c r="C4" t="n">
-        <v>5200</v>
+        <v>4678</v>
       </c>
       <c r="D4" t="n">
-        <v>9267</v>
+        <v>8427</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2536</v>
+        <v>1050</v>
       </c>
       <c r="C5" t="n">
-        <v>6202</v>
+        <v>5068</v>
       </c>
       <c r="D5" t="n">
-        <v>4593</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1257</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>5462</v>
+        <v>4922</v>
       </c>
       <c r="D6" t="n">
-        <v>1634</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>3386</v>
+        <v>2415</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1654</v>
+        <v>746</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>585</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3055</v>
+        <v>1060</v>
       </c>
       <c r="C2" t="n">
-        <v>3927</v>
+        <v>6852</v>
       </c>
       <c r="D2" t="n">
-        <v>12491</v>
+        <v>7304</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3258</v>
+        <v>422</v>
       </c>
       <c r="C3" t="n">
-        <v>4077</v>
+        <v>2879</v>
       </c>
       <c r="D3" t="n">
-        <v>12091</v>
+        <v>7055</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3416</v>
+        <v>806</v>
       </c>
       <c r="C4" t="n">
-        <v>4470</v>
+        <v>4716</v>
       </c>
       <c r="D4" t="n">
-        <v>9555</v>
+        <v>8018</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2806</v>
+        <v>1018</v>
       </c>
       <c r="C5" t="n">
-        <v>5926</v>
+        <v>4745</v>
       </c>
       <c r="D5" t="n">
-        <v>5035</v>
+        <v>5254</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1498</v>
+        <v>657</v>
       </c>
       <c r="C6" t="n">
-        <v>5931</v>
+        <v>4991</v>
       </c>
       <c r="D6" t="n">
-        <v>1946</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>212</v>
       </c>
       <c r="C7" t="n">
-        <v>4166</v>
+        <v>3739</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>2116</v>
+        <v>1570</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>720</v>
+        <v>497</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5721</v>
+        <v>1400</v>
       </c>
       <c r="C2" t="n">
-        <v>6198</v>
+        <v>5937</v>
       </c>
       <c r="D2" t="n">
-        <v>23510</v>
+        <v>12458</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2674</v>
+        <v>592</v>
       </c>
       <c r="C3" t="n">
-        <v>3550</v>
+        <v>4285</v>
       </c>
       <c r="D3" t="n">
-        <v>11349</v>
+        <v>6596</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2917</v>
+        <v>543</v>
       </c>
       <c r="C4" t="n">
-        <v>4199</v>
+        <v>3630</v>
       </c>
       <c r="D4" t="n">
-        <v>9654</v>
+        <v>7598</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2784</v>
+        <v>845</v>
       </c>
       <c r="C5" t="n">
-        <v>5173</v>
+        <v>4631</v>
       </c>
       <c r="D5" t="n">
-        <v>5532</v>
+        <v>5521</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1824</v>
+        <v>762</v>
       </c>
       <c r="C6" t="n">
-        <v>5875</v>
+        <v>4814</v>
       </c>
       <c r="D6" t="n">
-        <v>2335</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>662</v>
+        <v>368</v>
       </c>
       <c r="C7" t="n">
-        <v>4914</v>
+        <v>4350</v>
       </c>
       <c r="D7" t="n">
-        <v>902</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>2878</v>
+        <v>2589</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>1219</v>
+        <v>980</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>397</v>
+        <v>327</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4144</v>
+        <v>6482</v>
       </c>
       <c r="C2" t="n">
-        <v>5883</v>
+        <v>3516</v>
       </c>
       <c r="D2" t="n">
-        <v>5497</v>
+        <v>11308</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4001</v>
+        <v>1172</v>
       </c>
       <c r="C2" t="n">
-        <v>3421</v>
+        <v>6540</v>
       </c>
       <c r="D2" t="n">
-        <v>17304</v>
+        <v>10872</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3767</v>
+        <v>774</v>
       </c>
       <c r="C3" t="n">
-        <v>4502</v>
+        <v>4437</v>
       </c>
       <c r="D3" t="n">
-        <v>12955</v>
+        <v>6949</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4034</v>
+        <v>484</v>
       </c>
       <c r="C4" t="n">
-        <v>5963</v>
+        <v>3875</v>
       </c>
       <c r="D4" t="n">
-        <v>9986</v>
+        <v>7130</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1813</v>
+        <v>665</v>
       </c>
       <c r="C5" t="n">
-        <v>7967</v>
+        <v>4019</v>
       </c>
       <c r="D5" t="n">
-        <v>5157</v>
+        <v>5692</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>611</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>6082</v>
+        <v>4681</v>
       </c>
       <c r="D6" t="n">
-        <v>1927</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>485</v>
       </c>
       <c r="C7" t="n">
-        <v>2820</v>
+        <v>4557</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>1194</v>
+        <v>3321</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>1657</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
+        <v>589</v>
+      </c>
+      <c r="D10" t="n">
         <v>164</v>
-      </c>
-      <c r="D10" t="n">
-        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6647</v>
+        <v>7441</v>
       </c>
       <c r="C2" t="n">
-        <v>4668</v>
+        <v>8845</v>
       </c>
       <c r="D2" t="n">
-        <v>20978</v>
+        <v>20297</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1762</v>
+        <v>2139</v>
       </c>
       <c r="C3" t="n">
-        <v>3012</v>
+        <v>1388</v>
       </c>
       <c r="D3" t="n">
-        <v>1606</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5284</v>
+        <v>3992</v>
       </c>
       <c r="C2" t="n">
-        <v>4974</v>
+        <v>4517</v>
       </c>
       <c r="D2" t="n">
-        <v>18363</v>
+        <v>16075</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3447</v>
+        <v>4052</v>
       </c>
       <c r="C3" t="n">
-        <v>3443</v>
+        <v>5065</v>
       </c>
       <c r="D3" t="n">
-        <v>4742</v>
+        <v>5188</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>799</v>
+        <v>1013</v>
       </c>
       <c r="C4" t="n">
-        <v>1807</v>
+        <v>913</v>
       </c>
       <c r="D4" t="n">
-        <v>1504</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5908</v>
+        <v>2324</v>
       </c>
       <c r="C2" t="n">
-        <v>6118</v>
+        <v>3398</v>
       </c>
       <c r="D2" t="n">
-        <v>18914</v>
+        <v>15211</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3569</v>
+        <v>3317</v>
       </c>
       <c r="C3" t="n">
-        <v>3702</v>
+        <v>4075</v>
       </c>
       <c r="D3" t="n">
-        <v>6579</v>
+        <v>6635</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1793</v>
+        <v>2226</v>
       </c>
       <c r="C4" t="n">
-        <v>2696</v>
+        <v>3405</v>
       </c>
       <c r="D4" t="n">
-        <v>2079</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>389</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>1081</v>
+        <v>615</v>
       </c>
       <c r="D5" t="n">
-        <v>1196</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5467</v>
+        <v>2347</v>
       </c>
       <c r="C2" t="n">
-        <v>6482</v>
+        <v>5809</v>
       </c>
       <c r="D2" t="n">
-        <v>17489</v>
+        <v>25704</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3833</v>
+        <v>2342</v>
       </c>
       <c r="C3" t="n">
-        <v>4317</v>
+        <v>3195</v>
       </c>
       <c r="D3" t="n">
-        <v>7990</v>
+        <v>7529</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2254</v>
+        <v>2399</v>
       </c>
       <c r="C4" t="n">
-        <v>3190</v>
+        <v>3720</v>
       </c>
       <c r="D4" t="n">
-        <v>2816</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>903</v>
+        <v>1144</v>
       </c>
       <c r="C5" t="n">
-        <v>1911</v>
+        <v>2155</v>
       </c>
       <c r="D5" t="n">
-        <v>1320</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>692</v>
+        <v>447</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7460</v>
+        <v>3265</v>
       </c>
       <c r="C2" t="n">
-        <v>4628</v>
+        <v>5515</v>
       </c>
       <c r="D2" t="n">
-        <v>14966</v>
+        <v>27312</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3383</v>
+        <v>1958</v>
       </c>
       <c r="C3" t="n">
-        <v>4457</v>
+        <v>3967</v>
       </c>
       <c r="D3" t="n">
-        <v>8346</v>
+        <v>9761</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1901</v>
+        <v>2041</v>
       </c>
       <c r="C4" t="n">
-        <v>3134</v>
+        <v>3355</v>
       </c>
       <c r="D4" t="n">
-        <v>3182</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>817</v>
+        <v>1532</v>
       </c>
       <c r="C5" t="n">
-        <v>1877</v>
+        <v>2936</v>
       </c>
       <c r="D5" t="n">
-        <v>1259</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>270</v>
+        <v>603</v>
       </c>
       <c r="C6" t="n">
-        <v>888</v>
+        <v>1306</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5921</v>
+        <v>4002</v>
       </c>
       <c r="C2" t="n">
-        <v>3885</v>
+        <v>8474</v>
       </c>
       <c r="D2" t="n">
-        <v>16561</v>
+        <v>22399</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4548</v>
+        <v>2092</v>
       </c>
       <c r="C3" t="n">
-        <v>3904</v>
+        <v>4134</v>
       </c>
       <c r="D3" t="n">
-        <v>8883</v>
+        <v>11616</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2333</v>
+        <v>1741</v>
       </c>
       <c r="C4" t="n">
-        <v>3894</v>
+        <v>3602</v>
       </c>
       <c r="D4" t="n">
-        <v>4175</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1212</v>
+        <v>1568</v>
       </c>
       <c r="C5" t="n">
-        <v>2598</v>
+        <v>3084</v>
       </c>
       <c r="D5" t="n">
-        <v>1596</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>512</v>
+        <v>928</v>
       </c>
       <c r="C6" t="n">
-        <v>1455</v>
+        <v>2062</v>
       </c>
       <c r="D6" t="n">
-        <v>850</v>
+        <v>989</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="C7" t="n">
-        <v>654</v>
+        <v>819</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4442</v>
+        <v>3522</v>
       </c>
       <c r="C2" t="n">
-        <v>9297</v>
+        <v>5152</v>
       </c>
       <c r="D2" t="n">
-        <v>21373</v>
+        <v>17493</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4314</v>
+        <v>2944</v>
       </c>
       <c r="C3" t="n">
-        <v>3357</v>
+        <v>6736</v>
       </c>
       <c r="D3" t="n">
-        <v>9519</v>
+        <v>12857</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2989</v>
+        <v>1448</v>
       </c>
       <c r="C4" t="n">
-        <v>3818</v>
+        <v>5277</v>
       </c>
       <c r="D4" t="n">
-        <v>4997</v>
+        <v>4376</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1567</v>
+        <v>857</v>
       </c>
       <c r="C5" t="n">
-        <v>3278</v>
+        <v>2020</v>
       </c>
       <c r="D5" t="n">
-        <v>2042</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>781</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>2063</v>
+        <v>802</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>1085</v>
+        <v>326</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>473</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
